--- a/exports/gilt/gilt_overallStats.xlsx
+++ b/exports/gilt/gilt_overallStats.xlsx
@@ -514,13 +514,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5702</v>
+        <v>0.6458</v>
       </c>
       <c r="E3" s="4">
-        <v>1.563</v>
+        <v>2.3659</v>
       </c>
       <c r="F3" s="5">
-        <v>577</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.5" customHeight="1">
@@ -531,13 +531,13 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3859</v>
+        <v>0.3691</v>
       </c>
       <c r="E4" s="4">
-        <v>1.689</v>
+        <v>1.6414</v>
       </c>
       <c r="F4" s="5">
-        <v>7403</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.5" customHeight="1">
@@ -548,13 +548,13 @@
         <v>3</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4878</v>
+        <v>0.5178</v>
       </c>
       <c r="E5" s="4">
-        <v>2.0501</v>
+        <v>1.925</v>
       </c>
       <c r="F5" s="5">
-        <v>2005</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.5" customHeight="1">
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <v>0.417</v>
+        <v>0.4106</v>
       </c>
       <c r="E6" s="4">
-        <v>1.7543</v>
+        <v>1.7313</v>
       </c>
       <c r="F6" s="5">
-        <v>9985</v>
+        <v>5024</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="5" customHeight="1"/>
